--- a/artfynd/A 55745-2021 artfynd.xlsx
+++ b/artfynd/A 55745-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55745-2021 artfynd.xlsx
+++ b/artfynd/A 55745-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112605746</v>
+        <v>112752746</v>
       </c>
       <c r="B10" t="n">
-        <v>78919</v>
+        <v>74647</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,37 +1627,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillholmträsk, Vb</t>
+          <t>grandominerad naturskog, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698651</v>
+        <v>698539</v>
       </c>
       <c r="R10" t="n">
-        <v>7221367</v>
+        <v>7221311</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,17 +1681,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,866 +1701,15 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112605745</v>
-      </c>
-      <c r="B11" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>698657</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7221378</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112605749</v>
-      </c>
-      <c r="B12" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>698726</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7221324</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112605748</v>
-      </c>
-      <c r="B13" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>698725</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7221370</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112605747</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>698690</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7221351</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112605744</v>
-      </c>
-      <c r="B15" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>698657</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7221343</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112605751</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>698765</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7221290</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112605750</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Lillholmträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>698746</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7221283</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112752746</v>
-      </c>
-      <c r="B18" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>grandominerad naturskog, Vb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>698539</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7221311</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Inventering av rikkärr i Västerbottens län 2023</t>
         </is>
